--- a/data/trans_orig/IP31C_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>112995</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120877</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>104364</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97365</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108869</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>132109</t>
+          <t>107486</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126767</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134688</t>
+          <t>112872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>236473</t>
+          <t>225544</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>217465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242101</t>
+          <t>231915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>904</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,92 +848,92 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8474</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9159</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16319</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122478</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>241076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>195225</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>183525</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203697</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>169274</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>161736</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>175027</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>212335</t>
+          <t>162981</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201693</t>
+          <t>154978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221674</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>381609</t>
+          <t>358205</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368557</t>
+          <t>344542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392984</t>
+          <t>369574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6310</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12596</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14212</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29951</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21850</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41058</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14386</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8795</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21066</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55041</t>
+          <t>57487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>185210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>179813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>431337</t>
+          <t>409720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152056</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>144188</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157599</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>91,31%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>153216</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>96122</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>180704</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>81,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>168119</t>
+          <t>143678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160304</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174020</t>
+          <t>148976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>321336</t>
+          <t>295734</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252753</t>
+          <t>284718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>348522</t>
+          <t>303776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28114</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86797</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102939</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14466</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22334</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2460</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11524</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>187580</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>146416</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>138268</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>152939</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>143631</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>135087</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>150022</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>157064</t>
+          <t>142641</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>134447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163460</t>
+          <t>149454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>300695</t>
+          <t>289057</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289923</t>
+          <t>279042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310040</t>
+          <t>298844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -2206,67 +2206,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1761</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5634</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17828</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11532</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26071</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18245</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12505</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26804</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>46443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>163972</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>329677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>611755</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>594838</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>624783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>839</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>570485</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>478345</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>600018</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>669628</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>653190</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>683723</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1240114</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143772</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1271892</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>140049</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>65760</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53259</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>81355</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>48040</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>36228</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>61083</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>99650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>137397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
